--- a/rollforever/Assets/Excels/BuffConfig.xlsx
+++ b/rollforever/Assets/Excels/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\rollforever\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76808A9A-7DD9-4EE8-9251-3CC4ED5C9E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A3C072-EEAC-4416-9837-FB3B6335FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1097" yWindow="1097" windowWidth="12343" windowHeight="7012" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4250" yWindow="1270" windowWidth="14400" windowHeight="8210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="13">
   <si>
     <t>buffId</t>
   </si>
@@ -52,13 +52,25 @@
   </si>
   <si>
     <t>-1</t>
+  </si>
+  <si>
+    <t>CriticalRate</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>CriticalDamage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +83,12 @@
       <color rgb="FF202020"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -380,29 +398,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:R16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.84375" customWidth="1"/>
-    <col min="4" max="4" width="17.3046875" customWidth="1"/>
-    <col min="5" max="5" width="16.69140625" customWidth="1"/>
-    <col min="6" max="6" width="18.3046875" customWidth="1"/>
-    <col min="7" max="7" width="19.3828125" customWidth="1"/>
-    <col min="8" max="8" width="21.4609375" customWidth="1"/>
-    <col min="9" max="9" width="19.921875" customWidth="1"/>
-    <col min="10" max="10" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.23046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.61328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.3828125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" customWidth="1"/>
+    <col min="8" max="8" width="21.453125" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" customWidth="1"/>
+    <col min="10" max="10" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -434,7 +452,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -455,7 +473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -476,7 +494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -497,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -518,7 +536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -539,7 +557,218 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.CONCAT(3, B7, A7)</f>
+        <v>3102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" ref="C8:C11" si="1">_xlfn.CONCAT(3, B8, A8)</f>
+        <v>3202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>3302</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>0.15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>3402</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>3502</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <f>_xlfn.CONCAT(3, B12, A12)</f>
+        <v>3103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" ref="C13:C16" si="2">_xlfn.CONCAT(3, B13, A13)</f>
+        <v>3203</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="2"/>
+        <v>3303</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>0.15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="2"/>
+        <v>3403</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="2"/>
+        <v>3503</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
